--- a/check_outputs/fu_all_regions/fu_report_report_units.xlsx
+++ b/check_outputs/fu_all_regions/fu_report_report_units.xlsx
@@ -418,223 +418,168 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>FU</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>PN</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>PN</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>PP</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>DIN</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Bananas</t>
-        </is>
+      <c r="A2" t="n">
+        <v>0.6343897184545403</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6343897184545403</v>
+        <v>0.1496872154804894</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1496872154804894</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
+        <v>15.27851137732809</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>659.1688991268893</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4518.817964091623</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1095.102719435532</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1747.172720247471</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1.138384037436374</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2.793101865307794</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.400970374155399</v>
+      </c>
+      <c r="D4" t="n">
+        <v>17.26090006076216</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.4227001540009779</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2.757372192615153</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.281360446407607</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5.252489134521352</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>52.74070105767262</v>
+      </c>
+      <c r="B6" t="n">
+        <v>374.8097391298421</v>
+      </c>
+      <c r="C6" t="n">
+        <v>119.2691331584189</v>
+      </c>
+      <c r="D6" t="n">
+        <v>187.5566073051575</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>449.7162769234506</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1440.237137291243</v>
+      </c>
+      <c r="C7" t="n">
+        <v>754.6309991490632</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1986.881337989322</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1.951620443357241</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1.444595202735199</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8913196472517017</v>
+      </c>
+      <c r="D8" t="n">
+        <v>12.81429851044728</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>657.9210798366488</v>
+      </c>
+      <c r="B9" t="n">
+        <v>787.2729435823198</v>
+      </c>
+      <c r="C9" t="n">
+        <v>451.0306682166557</v>
+      </c>
+      <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="n">
-        <v>15.27851137732809</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Conservation</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>659.1688991268893</v>
-      </c>
-      <c r="C3" t="n">
-        <v>4518.817964091623</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1095.102719435532</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1747.172720247471</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cropping</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1.138384037436374</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2.793101865307794</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.400970374155399</v>
-      </c>
-      <c r="E4" t="n">
-        <v>17.26090006076216</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Dairy</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.4227001540009779</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2.757372192615153</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.281360446407607</v>
-      </c>
-      <c r="E5" t="n">
-        <v>5.252489134521352</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Forestry</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>52.74070105767262</v>
-      </c>
-      <c r="C6" t="n">
-        <v>374.8097391298421</v>
-      </c>
-      <c r="D6" t="n">
-        <v>119.2691331584189</v>
-      </c>
-      <c r="E6" t="n">
-        <v>187.5566073051575</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Grazing</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>449.7162769234506</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1440.237137291243</v>
-      </c>
-      <c r="D7" t="n">
-        <v>754.6309991490632</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1986.881337989322</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Horticulture</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.951620443357241</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1.444595202735199</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.8913196472517017</v>
-      </c>
-      <c r="E8" t="n">
-        <v>12.81429851044728</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Stream</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>657.9210798366488</v>
-      </c>
-      <c r="C9" t="n">
-        <v>787.2729435823198</v>
-      </c>
-      <c r="D9" t="n">
-        <v>451.0306682166557</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sugarcane</t>
-        </is>
+      <c r="A10" t="n">
+        <v>9.378492537122382</v>
       </c>
       <c r="B10" t="n">
-        <v>9.378492537122382</v>
+        <v>13.81419385750302</v>
       </c>
       <c r="C10" t="n">
-        <v>13.81419385750302</v>
+        <v>13.34997067530239</v>
       </c>
       <c r="D10" t="n">
-        <v>13.34997067530239</v>
-      </c>
-      <c r="E10" t="n">
         <v>208.6707959253923</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Urban + Other</t>
-        </is>
+      <c r="A11" t="n">
+        <v>11.3465128931134</v>
       </c>
       <c r="B11" t="n">
-        <v>11.3465128931134</v>
+        <v>12.54166183242452</v>
       </c>
       <c r="C11" t="n">
-        <v>12.54166183242452</v>
+        <v>5.39123158262644</v>
       </c>
       <c r="D11" t="n">
-        <v>5.39123158262644</v>
-      </c>
-      <c r="E11" t="n">
         <v>101.8426519016315</v>
       </c>
     </row>
@@ -649,223 +594,168 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>FU</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>PN</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>PN</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>PP</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>DIN</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Bananas</t>
-        </is>
+      <c r="A2" t="n">
+        <v>7.324460073688767</v>
       </c>
       <c r="B2" t="n">
-        <v>7.324460073688767</v>
+        <v>38.58358604712525</v>
       </c>
       <c r="C2" t="n">
-        <v>38.58358604712525</v>
+        <v>32.66250550013394</v>
       </c>
       <c r="D2" t="n">
-        <v>32.66250550013394</v>
-      </c>
-      <c r="E2" t="n">
         <v>671.0366040129064</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Conservation</t>
-        </is>
+      <c r="A3" t="n">
+        <v>888.0547216259314</v>
       </c>
       <c r="B3" t="n">
-        <v>888.0547216259314</v>
+        <v>4686.547081714216</v>
       </c>
       <c r="C3" t="n">
-        <v>4686.547081714216</v>
+        <v>1181.181376087148</v>
       </c>
       <c r="D3" t="n">
-        <v>1181.181376087148</v>
-      </c>
-      <c r="E3" t="n">
         <v>1740.93011042808</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cropping</t>
-        </is>
+      <c r="A4" t="n">
+        <v>99.80485895615267</v>
       </c>
       <c r="B4" t="n">
-        <v>99.80485895615267</v>
+        <v>429.8371724753187</v>
       </c>
       <c r="C4" t="n">
-        <v>429.8371724753187</v>
+        <v>174.7049981863196</v>
       </c>
       <c r="D4" t="n">
-        <v>174.7049981863196</v>
-      </c>
-      <c r="E4" t="n">
         <v>136.1518160022904</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Dairy</t>
-        </is>
+      <c r="A5" t="n">
+        <v>10.35183082409657</v>
       </c>
       <c r="B5" t="n">
-        <v>10.35183082409657</v>
+        <v>72.95474696438471</v>
       </c>
       <c r="C5" t="n">
-        <v>72.95474696438471</v>
+        <v>32.87094984804134</v>
       </c>
       <c r="D5" t="n">
-        <v>32.87094984804134</v>
-      </c>
-      <c r="E5" t="n">
         <v>18.5388138676391</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Forestry</t>
-        </is>
+      <c r="A6" t="n">
+        <v>83.57816576537267</v>
       </c>
       <c r="B6" t="n">
-        <v>83.57816576537267</v>
+        <v>396.2976917925974</v>
       </c>
       <c r="C6" t="n">
-        <v>396.2976917925974</v>
+        <v>129.7321375576619</v>
       </c>
       <c r="D6" t="n">
-        <v>129.7321375576619</v>
-      </c>
-      <c r="E6" t="n">
         <v>239.6654308780441</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Grazing</t>
-        </is>
+      <c r="A7" t="n">
+        <v>4393.10020687869</v>
       </c>
       <c r="B7" t="n">
-        <v>4393.10020687869</v>
+        <v>8692.353378322548</v>
       </c>
       <c r="C7" t="n">
-        <v>8692.353378322548</v>
+        <v>4200.784441663612</v>
       </c>
       <c r="D7" t="n">
-        <v>4200.784441663612</v>
-      </c>
-      <c r="E7" t="n">
         <v>2353.778508312657</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Horticulture</t>
-        </is>
+      <c r="A8" t="n">
+        <v>42.75104321407468</v>
       </c>
       <c r="B8" t="n">
-        <v>42.75104321407468</v>
+        <v>75.62317531289301</v>
       </c>
       <c r="C8" t="n">
-        <v>75.62317531289301</v>
+        <v>38.74840679362379</v>
       </c>
       <c r="D8" t="n">
-        <v>38.74840679362379</v>
-      </c>
-      <c r="E8" t="n">
         <v>174.6076336783581</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Stream</t>
-        </is>
+      <c r="A9" t="n">
+        <v>1897.837446914873</v>
       </c>
       <c r="B9" t="n">
-        <v>1897.837446914873</v>
+        <v>2351.605336430832</v>
       </c>
       <c r="C9" t="n">
-        <v>2351.605336430832</v>
+        <v>1356.501285438728</v>
       </c>
       <c r="D9" t="n">
-        <v>1356.501285438728</v>
-      </c>
-      <c r="E9" t="n">
         <v>188.9008148904195</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sugarcane</t>
-        </is>
+      <c r="A10" t="n">
+        <v>119.3457388823318</v>
       </c>
       <c r="B10" t="n">
-        <v>119.3457388823318</v>
+        <v>1152.94403223683</v>
       </c>
       <c r="C10" t="n">
-        <v>1152.94403223683</v>
+        <v>267.2955876953052</v>
       </c>
       <c r="D10" t="n">
-        <v>267.2955876953052</v>
-      </c>
-      <c r="E10" t="n">
         <v>3333.155755264661</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Urban + Other</t>
-        </is>
+      <c r="A11" t="n">
+        <v>67.28758039551032</v>
       </c>
       <c r="B11" t="n">
-        <v>67.28758039551032</v>
+        <v>67.63575219109575</v>
       </c>
       <c r="C11" t="n">
-        <v>67.63575219109575</v>
+        <v>23.72517209180274</v>
       </c>
       <c r="D11" t="n">
-        <v>23.72517209180274</v>
-      </c>
-      <c r="E11" t="n">
         <v>437.1871324313666</v>
       </c>
     </row>
@@ -880,223 +770,168 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>FU</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>PN</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>PN</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>PP</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>DIN</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Bananas</t>
-        </is>
+      <c r="A2" t="n">
+        <v>7.014665407755857</v>
       </c>
       <c r="B2" t="n">
-        <v>7.014665407755857</v>
+        <v>36.61129222464432</v>
       </c>
       <c r="C2" t="n">
-        <v>36.61129222464432</v>
+        <v>31.87424553547741</v>
       </c>
       <c r="D2" t="n">
-        <v>31.87424553547741</v>
-      </c>
-      <c r="E2" t="n">
         <v>616.4881640459724</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Conservation</t>
-        </is>
+      <c r="A3" t="n">
+        <v>887.5967011442177</v>
       </c>
       <c r="B3" t="n">
-        <v>887.5967011442177</v>
+        <v>4685.537304651231</v>
       </c>
       <c r="C3" t="n">
-        <v>4685.537304651231</v>
+        <v>1180.276765942709</v>
       </c>
       <c r="D3" t="n">
-        <v>1180.276765942709</v>
-      </c>
-      <c r="E3" t="n">
         <v>1741.228227996026</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cropping</t>
-        </is>
+      <c r="A4" t="n">
+        <v>95.6168558310741</v>
       </c>
       <c r="B4" t="n">
-        <v>95.6168558310741</v>
+        <v>407.186234682017</v>
       </c>
       <c r="C4" t="n">
-        <v>407.186234682017</v>
+        <v>167.6940613257314</v>
       </c>
       <c r="D4" t="n">
-        <v>167.6940613257314</v>
-      </c>
-      <c r="E4" t="n">
         <v>136.2051262952476</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Dairy</t>
-        </is>
+      <c r="A5" t="n">
+        <v>10.36621646460539</v>
       </c>
       <c r="B5" t="n">
-        <v>10.36621646460539</v>
+        <v>72.99690269753249</v>
       </c>
       <c r="C5" t="n">
-        <v>72.99690269753249</v>
+        <v>32.89454705854402</v>
       </c>
       <c r="D5" t="n">
-        <v>32.89454705854402</v>
-      </c>
-      <c r="E5" t="n">
         <v>18.5376359078662</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Forestry</t>
-        </is>
+      <c r="A6" t="n">
+        <v>83.27339114293156</v>
       </c>
       <c r="B6" t="n">
-        <v>83.27339114293156</v>
+        <v>394.4757534825252</v>
       </c>
       <c r="C6" t="n">
-        <v>394.4757534825252</v>
+        <v>127.8615921180481</v>
       </c>
       <c r="D6" t="n">
-        <v>127.8615921180481</v>
-      </c>
-      <c r="E6" t="n">
         <v>239.7120795808185</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Grazing</t>
-        </is>
+      <c r="A7" t="n">
+        <v>4365.486252933503</v>
       </c>
       <c r="B7" t="n">
-        <v>4365.486252933503</v>
+        <v>8635.236840492889</v>
       </c>
       <c r="C7" t="n">
-        <v>8635.236840492889</v>
+        <v>4157.682478710645</v>
       </c>
       <c r="D7" t="n">
-        <v>4157.682478710645</v>
-      </c>
-      <c r="E7" t="n">
         <v>2354.938360888102</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Horticulture</t>
-        </is>
+      <c r="A8" t="n">
+        <v>42.75992011067672</v>
       </c>
       <c r="B8" t="n">
-        <v>42.75992011067672</v>
+        <v>75.62769334456536</v>
       </c>
       <c r="C8" t="n">
-        <v>75.62769334456536</v>
+        <v>38.74987823804567</v>
       </c>
       <c r="D8" t="n">
-        <v>38.74987823804567</v>
-      </c>
-      <c r="E8" t="n">
         <v>174.6147443486879</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Stream</t>
-        </is>
+      <c r="A9" t="n">
+        <v>1829.754150967294</v>
       </c>
       <c r="B9" t="n">
-        <v>1829.754150967294</v>
+        <v>2225.219505408603</v>
       </c>
       <c r="C9" t="n">
-        <v>2225.219505408603</v>
+        <v>1298.893663931279</v>
       </c>
       <c r="D9" t="n">
-        <v>1298.893663931279</v>
-      </c>
-      <c r="E9" t="n">
         <v>188.9171595079518</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sugarcane</t>
-        </is>
+      <c r="A10" t="n">
+        <v>116.5847260789308</v>
       </c>
       <c r="B10" t="n">
-        <v>116.5847260789308</v>
+        <v>1129.391771362264</v>
       </c>
       <c r="C10" t="n">
-        <v>1129.391771362264</v>
+        <v>263.0381322588676</v>
       </c>
       <c r="D10" t="n">
-        <v>263.0381322588676</v>
-      </c>
-      <c r="E10" t="n">
         <v>3199.558357587086</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Urban + Other</t>
-        </is>
+      <c r="A11" t="n">
+        <v>67.35525243475313</v>
       </c>
       <c r="B11" t="n">
-        <v>67.35525243475313</v>
+        <v>67.6872887830863</v>
       </c>
       <c r="C11" t="n">
-        <v>67.6872887830863</v>
+        <v>23.74781329349908</v>
       </c>
       <c r="D11" t="n">
-        <v>23.74781329349908</v>
-      </c>
-      <c r="E11" t="n">
         <v>437.1839967110171</v>
       </c>
     </row>
@@ -1111,223 +946,168 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>FU</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>PN</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>PN</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>PP</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>DIN</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Bananas</t>
-        </is>
+      <c r="A2" t="n">
+        <v>6.690070355234227</v>
       </c>
       <c r="B2" t="n">
-        <v>6.690070355234227</v>
+        <v>38.43389883164476</v>
       </c>
       <c r="C2" t="n">
-        <v>38.43389883164476</v>
+        <v>32.66250550013394</v>
       </c>
       <c r="D2" t="n">
-        <v>32.66250550013394</v>
-      </c>
-      <c r="E2" t="n">
         <v>655.7580926355784</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Conservation</t>
-        </is>
+      <c r="A3" t="n">
+        <v>228.8858224990421</v>
       </c>
       <c r="B3" t="n">
-        <v>228.8858224990421</v>
+        <v>167.7291176225926</v>
       </c>
       <c r="C3" t="n">
-        <v>167.7291176225926</v>
+        <v>86.07865665161603</v>
       </c>
       <c r="D3" t="n">
-        <v>86.07865665161603</v>
-      </c>
-      <c r="E3" t="n">
         <v>-6.242609819390509</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cropping</t>
-        </is>
+      <c r="A4" t="n">
+        <v>98.6664749187163</v>
       </c>
       <c r="B4" t="n">
-        <v>98.6664749187163</v>
+        <v>427.0440706100109</v>
       </c>
       <c r="C4" t="n">
-        <v>427.0440706100109</v>
+        <v>173.3040278121642</v>
       </c>
       <c r="D4" t="n">
-        <v>173.3040278121642</v>
-      </c>
-      <c r="E4" t="n">
         <v>118.8909159415282</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Dairy</t>
-        </is>
+      <c r="A5" t="n">
+        <v>9.929130670095594</v>
       </c>
       <c r="B5" t="n">
-        <v>9.929130670095594</v>
+        <v>70.19737477176956</v>
       </c>
       <c r="C5" t="n">
-        <v>70.19737477176956</v>
+        <v>31.58958940163373</v>
       </c>
       <c r="D5" t="n">
-        <v>31.58958940163373</v>
-      </c>
-      <c r="E5" t="n">
         <v>13.28632473311775</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Forestry</t>
-        </is>
+      <c r="A6" t="n">
+        <v>30.83746470770006</v>
       </c>
       <c r="B6" t="n">
-        <v>30.83746470770006</v>
+        <v>21.48795266275528</v>
       </c>
       <c r="C6" t="n">
-        <v>21.48795266275528</v>
+        <v>10.46300439924299</v>
       </c>
       <c r="D6" t="n">
-        <v>10.46300439924299</v>
-      </c>
-      <c r="E6" t="n">
         <v>52.10882357288662</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Grazing</t>
-        </is>
+      <c r="A7" t="n">
+        <v>3943.38392995524</v>
       </c>
       <c r="B7" t="n">
-        <v>3943.38392995524</v>
+        <v>7252.116241031305</v>
       </c>
       <c r="C7" t="n">
-        <v>7252.116241031305</v>
+        <v>3446.153442514548</v>
       </c>
       <c r="D7" t="n">
-        <v>3446.153442514548</v>
-      </c>
-      <c r="E7" t="n">
         <v>366.8971703233351</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Horticulture</t>
-        </is>
+      <c r="A8" t="n">
+        <v>40.79942277071744</v>
       </c>
       <c r="B8" t="n">
-        <v>40.79942277071744</v>
+        <v>74.17858011015781</v>
       </c>
       <c r="C8" t="n">
-        <v>74.17858011015781</v>
+        <v>37.85708714637209</v>
       </c>
       <c r="D8" t="n">
-        <v>37.85708714637209</v>
-      </c>
-      <c r="E8" t="n">
         <v>161.7933351679108</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Stream</t>
-        </is>
+      <c r="A9" t="n">
+        <v>1239.916367078224</v>
       </c>
       <c r="B9" t="n">
-        <v>1239.916367078224</v>
+        <v>1564.332392848512</v>
       </c>
       <c r="C9" t="n">
-        <v>1564.332392848512</v>
+        <v>905.4706172220718</v>
       </c>
       <c r="D9" t="n">
-        <v>905.4706172220718</v>
-      </c>
-      <c r="E9" t="n">
         <v>188.9008148904195</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sugarcane</t>
-        </is>
+      <c r="A10" t="n">
+        <v>109.9672463452094</v>
       </c>
       <c r="B10" t="n">
-        <v>109.9672463452094</v>
+        <v>1139.129838379327</v>
       </c>
       <c r="C10" t="n">
-        <v>1139.129838379327</v>
+        <v>253.9456170200028</v>
       </c>
       <c r="D10" t="n">
-        <v>253.9456170200028</v>
-      </c>
-      <c r="E10" t="n">
         <v>3124.484959339269</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Urban + Other</t>
-        </is>
+      <c r="A11" t="n">
+        <v>55.94106750239692</v>
       </c>
       <c r="B11" t="n">
-        <v>55.94106750239692</v>
+        <v>55.09409035867123</v>
       </c>
       <c r="C11" t="n">
-        <v>55.09409035867123</v>
+        <v>18.3339405091763</v>
       </c>
       <c r="D11" t="n">
-        <v>18.3339405091763</v>
-      </c>
-      <c r="E11" t="n">
         <v>335.3444805297351</v>
       </c>
     </row>
@@ -1342,223 +1122,168 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>FU</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>PN</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>PN</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>PP</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>DIN</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Bananas</t>
-        </is>
+      <c r="A2" t="n">
+        <v>0.3097946659329098</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3097946659329098</v>
+        <v>1.972293822480935</v>
       </c>
       <c r="C2" t="n">
-        <v>1.972293822480935</v>
+        <v>0.7882599646565254</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7882599646565254</v>
-      </c>
-      <c r="E2" t="n">
         <v>54.54843996693398</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Conservation</t>
-        </is>
+      <c r="A3" t="n">
+        <v>0.4580204817136746</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4580204817136746</v>
+        <v>1.00977706298454</v>
       </c>
       <c r="C3" t="n">
-        <v>1.00977706298454</v>
+        <v>0.9046101444389478</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9046101444389478</v>
-      </c>
-      <c r="E3" t="n">
         <v>-0.2981175679462922</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cropping</t>
-        </is>
+      <c r="A4" t="n">
+        <v>4.188003125078566</v>
       </c>
       <c r="B4" t="n">
-        <v>4.188003125078566</v>
+        <v>22.65093779330175</v>
       </c>
       <c r="C4" t="n">
-        <v>22.65093779330175</v>
+        <v>7.010936860588174</v>
       </c>
       <c r="D4" t="n">
-        <v>7.010936860588174</v>
-      </c>
-      <c r="E4" t="n">
         <v>-0.05331029295720668</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Dairy</t>
-        </is>
+      <c r="A5" t="n">
+        <v>-0.01438564050881652</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.01438564050881652</v>
+        <v>-0.04215573314777998</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.04215573314777998</v>
+        <v>-0.02359721050267893</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.02359721050267893</v>
-      </c>
-      <c r="E5" t="n">
         <v>0.001177959772899584</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Forestry</t>
-        </is>
+      <c r="A6" t="n">
+        <v>0.3047746224411156</v>
       </c>
       <c r="B6" t="n">
-        <v>0.3047746224411156</v>
+        <v>1.821938310072142</v>
       </c>
       <c r="C6" t="n">
-        <v>1.821938310072142</v>
+        <v>1.870545439613821</v>
       </c>
       <c r="D6" t="n">
-        <v>1.870545439613821</v>
-      </c>
-      <c r="E6" t="n">
         <v>-0.04664870277440514</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Grazing</t>
-        </is>
+      <c r="A7" t="n">
+        <v>27.61395394518695</v>
       </c>
       <c r="B7" t="n">
-        <v>27.61395394518695</v>
+        <v>57.11653782965914</v>
       </c>
       <c r="C7" t="n">
-        <v>57.11653782965914</v>
+        <v>43.10196295296646</v>
       </c>
       <c r="D7" t="n">
-        <v>43.10196295296646</v>
-      </c>
-      <c r="E7" t="n">
         <v>-1.159852575444347</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Horticulture</t>
-        </is>
+      <c r="A8" t="n">
+        <v>-0.008876896602032502</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.008876896602032502</v>
+        <v>-0.004518031672347433</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.004518031672347433</v>
+        <v>-0.001471444421881074</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.001471444421881074</v>
-      </c>
-      <c r="E8" t="n">
         <v>-0.007110670329808499</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Stream</t>
-        </is>
+      <c r="A9" t="n">
+        <v>68.08329594757856</v>
       </c>
       <c r="B9" t="n">
-        <v>68.08329594757856</v>
+        <v>126.3858310222295</v>
       </c>
       <c r="C9" t="n">
-        <v>126.3858310222295</v>
+        <v>57.60762150744813</v>
       </c>
       <c r="D9" t="n">
-        <v>57.60762150744813</v>
-      </c>
-      <c r="E9" t="n">
         <v>-0.01634461753229743</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sugarcane</t>
-        </is>
+      <c r="A10" t="n">
+        <v>2.761012803400988</v>
       </c>
       <c r="B10" t="n">
-        <v>2.761012803400988</v>
+        <v>23.55226087456549</v>
       </c>
       <c r="C10" t="n">
-        <v>23.55226087456549</v>
+        <v>4.257455436437624</v>
       </c>
       <c r="D10" t="n">
-        <v>4.257455436437624</v>
-      </c>
-      <c r="E10" t="n">
         <v>133.5973976775749</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Urban + Other</t>
-        </is>
+      <c r="A11" t="n">
+        <v>-0.06767203924280807</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.06767203924280807</v>
+        <v>-0.05153659199055483</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.05153659199055483</v>
+        <v>-0.02264120169633799</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.02264120169633799</v>
-      </c>
-      <c r="E11" t="n">
         <v>0.003135720349519033</v>
       </c>
     </row>
@@ -1573,223 +1298,168 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>FU</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>PN</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>PN</t>
+          <t>PP</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>PP</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>DIN</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Bananas</t>
-        </is>
+      <c r="A2" t="n">
+        <v>4.630663796988777</v>
       </c>
       <c r="B2" t="n">
-        <v>4.630663796988777</v>
+        <v>5.131651699246906</v>
       </c>
       <c r="C2" t="n">
-        <v>5.131651699246906</v>
+        <v>2.413348126809479</v>
       </c>
       <c r="D2" t="n">
-        <v>2.413348126809479</v>
-      </c>
-      <c r="E2" t="n">
         <v>8.318378466012764</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Conservation</t>
-        </is>
+      <c r="A3" t="n">
+        <v>0.200108716526377</v>
       </c>
       <c r="B3" t="n">
-        <v>0.200108716526377</v>
+        <v>0.60202848336485</v>
       </c>
       <c r="C3" t="n">
-        <v>0.60202848336485</v>
+        <v>1.050911084846681</v>
       </c>
       <c r="D3" t="n">
-        <v>1.050911084846681</v>
-      </c>
-      <c r="E3" t="n">
         <v>4.775527809223204</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cropping</t>
-        </is>
+      <c r="A4" t="n">
+        <v>4.244606010834723</v>
       </c>
       <c r="B4" t="n">
-        <v>4.244606010834723</v>
+        <v>5.304121834766615</v>
       </c>
       <c r="C4" t="n">
-        <v>5.304121834766615</v>
+        <v>4.045455232112081</v>
       </c>
       <c r="D4" t="n">
-        <v>4.045455232112081</v>
-      </c>
-      <c r="E4" t="n">
         <v>-0.04483966881323822</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Dairy</t>
-        </is>
+      <c r="A5" t="n">
+        <v>-0.1448831824939416</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.1448831824939416</v>
+        <v>-0.06005314769225992</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.06005314769225992</v>
+        <v>-0.07469932642257941</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.07469932642257941</v>
-      </c>
-      <c r="E5" t="n">
         <v>0.008865956512137464</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Forestry</t>
-        </is>
+      <c r="A6" t="n">
+        <v>0.9883258086551259</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9883258086551259</v>
+        <v>8.478882742654575</v>
       </c>
       <c r="C6" t="n">
-        <v>8.478882742654575</v>
+        <v>17.8777086220967</v>
       </c>
       <c r="D6" t="n">
-        <v>17.8777086220967</v>
-      </c>
-      <c r="E6" t="n">
         <v>-0.08952169628077632</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Grazing</t>
-        </is>
+      <c r="A7" t="n">
+        <v>0.7002603458268997</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7002603458268997</v>
+        <v>0.7875844226889658</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7875844226889658</v>
+        <v>1.250726750040368</v>
       </c>
       <c r="D7" t="n">
-        <v>1.250726750040368</v>
-      </c>
-      <c r="E7" t="n">
         <v>-0.3161246990327576</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Horticulture</t>
-        </is>
+      <c r="A8" t="n">
+        <v>-0.02175740733372245</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.02175740733372245</v>
+        <v>-0.006090749736161027</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.006090749736161027</v>
+        <v>-0.003886840041844279</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.003886840041844279</v>
-      </c>
-      <c r="E8" t="n">
         <v>-0.004394909297363189</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Stream</t>
-        </is>
+      <c r="A9" t="n">
+        <v>5.490958725547925</v>
       </c>
       <c r="B9" t="n">
-        <v>5.490958725547925</v>
+        <v>8.079218432093702</v>
       </c>
       <c r="C9" t="n">
-        <v>8.079218432093702</v>
+        <v>6.362174587639825</v>
       </c>
       <c r="D9" t="n">
-        <v>6.362174587639825</v>
-      </c>
-      <c r="E9" t="n">
         <v>-0.008652486513506502</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sugarcane</t>
-        </is>
+      <c r="A10" t="n">
+        <v>2.510759244378649</v>
       </c>
       <c r="B10" t="n">
-        <v>2.510759244378649</v>
+        <v>2.067565968430252</v>
       </c>
       <c r="C10" t="n">
-        <v>2.067565968430252</v>
+        <v>1.676522511551074</v>
       </c>
       <c r="D10" t="n">
-        <v>1.676522511551074</v>
-      </c>
-      <c r="E10" t="n">
         <v>4.275821436689732</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Urban + Other</t>
-        </is>
+      <c r="A11" t="n">
+        <v>-0.1209702321821236</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.1209702321821236</v>
+        <v>-0.09354286758351661</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.09354286758351661</v>
+        <v>-0.1234933738603868</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1234933738603868</v>
-      </c>
-      <c r="E11" t="n">
         <v>0.0009350743881532259</v>
       </c>
     </row>
